--- a/output/pdf_financials_xlsx/DEX.xlsx
+++ b/output/pdf_financials_xlsx/DEX.xlsx
@@ -3056,25 +3056,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.06727</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.255624</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.92818</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.95908</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.462868</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.464618</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.550418</v>
       </c>
     </row>
     <row r="93">
@@ -5058,7 +5058,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>1.06727</v>
       </c>
@@ -5810,7 +5814,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>1.06727</v>
       </c>
@@ -6373,7 +6381,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DEX.xlsx
+++ b/output/pdf_financials_xlsx/DEX.xlsx
@@ -729,25 +729,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.054744</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.087294</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.017026</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.206523</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.6828959999999999</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.703585</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.382605</v>
       </c>
     </row>
     <row r="13">
@@ -1201,25 +1201,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.884989</v>
+        <v>-3.939733</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.087849</v>
+        <v>-1.175143</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>12.131902</v>
+        <v>12.114876</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.419306</v>
+        <v>3.212783</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.969491</v>
+        <v>-3.652387</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.819817</v>
+        <v>1.116232</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.785099</v>
+        <v>0.402494</v>
       </c>
     </row>
     <row r="28">
@@ -1257,25 +1257,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.830986</v>
+        <v>-3.88573</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.869357</v>
+        <v>-0.956651</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>12.340398</v>
+        <v>12.323372</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.647311</v>
+        <v>3.440788</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.71217</v>
+        <v>-3.395066</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.983316</v>
+        <v>1.279731</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.90546</v>
+        <v>0.522855</v>
       </c>
     </row>
     <row r="30">
@@ -1285,25 +1285,25 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-451.7810687591837</v>
+        <v>-458.2369270755943</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-82.13219837787025</v>
+        <v>-90.37926848278435</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>301.5638784067189</v>
+        <v>301.1478118751732</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>48.92197081188792</v>
+        <v>46.15184449746518</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-167.3587058404651</v>
+        <v>-209.4978751342889</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>189.9580588096134</v>
+        <v>122.5700879529462</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>71.30521476378465</v>
+        <v>41.17496970083562</v>
       </c>
     </row>
     <row r="31">
@@ -4653,7 +4653,11 @@
           <t>Reclamation deposit (Note 8)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -5520,7 +5524,11 @@
           <t>Reclamation deposit (Note 7)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -6124,7 +6132,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -8005,7 +8017,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
         <v>0.024181</v>
       </c>
@@ -10032,7 +10048,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">

--- a/output/pdf_financials_xlsx/DEX.xlsx
+++ b/output/pdf_financials_xlsx/DEX.xlsx
@@ -598,10 +598,10 @@
         <v>0.023488</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.027415</v>
+        <v>0.057415</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.028668</v>
+        <v>0.043668</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.027807</v>
@@ -875,13 +875,13 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.601342</v>
+        <v>-0.694005</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.22076</v>
+        <v>0.021599</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.200307</v>
+        <v>0.224901</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.181374</v>
@@ -1319,13 +1319,13 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>4.956700111820884</v>
+        <v>5.720496258542148</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6.456280894427115</v>
+        <v>0.6316778901917524</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-6.745499481224224</v>
+        <v>-7.573722230510212</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>9.966606532415073</v>
@@ -1460,25 +1460,25 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>0.34563</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>0.175985</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>0.705783</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>0.561844</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>0.121088</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>0.160818</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>0.165822</v>
       </c>
     </row>
     <row r="38">
@@ -1572,25 +1572,25 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>0.34563</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>0.175985</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>0.705783</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.561844</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.121088</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.160818</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.165822</v>
       </c>
     </row>
     <row r="42">
@@ -1768,25 +1768,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.989415</v>
+        <v>4.643785</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.254948</v>
+        <v>1.078963</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.587347</v>
+        <v>1.881564</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.742079</v>
+        <v>1.180235</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.250972</v>
+        <v>1.129884</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.275345</v>
+        <v>1.114527</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>12.864353</v>
+        <v>12.698531</v>
       </c>
     </row>
     <row r="49">
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.174487</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.01523</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7048,7 +7048,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -8830,7 +8834,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -9030,7 +9038,11 @@
           <t>Net proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E99" s="5" t="n">
         <v>0.174487</v>
       </c>
@@ -11207,7 +11219,11 @@
           <t>Current income tax recovery (Note 15 (a))</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -11450,7 +11466,11 @@
           <t>Directors’ fees (Note 12)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -11946,7 +11966,11 @@
           <t>Directors’ fees (Note 11)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -12342,7 +12366,11 @@
           <t>Current income tax recovery (Note 14 (a))</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -12648,7 +12676,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -13299,7 +13331,11 @@
           <t>Current income tax (recovery) expense (Note 13 (a))</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
